--- a/output/MULTIPLE_CANDIDATES_SUMMARY.xlsx
+++ b/output/MULTIPLE_CANDIDATES_SUMMARY.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
